--- a/ABA_mining/outputs/eval/task3/facility/llama3.2/zero_shot/EVAL_SUMMARY.xlsx
+++ b/ABA_mining/outputs/eval/task3/facility/llama3.2/zero_shot/EVAL_SUMMARY.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,10 +526,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -538,19 +538,19 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>342</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2</v>
+        <v>0.316</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.480243</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2</v>
+        <v>0.316</v>
       </c>
     </row>
     <row r="3">
@@ -571,12 +571,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Contrary(P)Body(P)</t>
+          <t>Contrary(N)Body(N)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Test 1</t>
+          <t>Test 2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>158</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -597,19 +597,255 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>342</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4</v>
+        <v>0.316</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5714285714285715</v>
+        <v>0.480243</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4</v>
+        <v>0.316</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>llama3.2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>zero_shot</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>facility</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Contrary(N)Body(N)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Test 3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>500</v>
+      </c>
+      <c r="H4" t="n">
+        <v>158</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>342</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.480243</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.316</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>llama3.2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>zero_shot</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>facility</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Contrary(P)Body(P)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Test 1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>500</v>
+      </c>
+      <c r="H5" t="n">
+        <v>144</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>356</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.447205</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.288</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>llama3.2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>zero_shot</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>facility</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Contrary(P)Body(P)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Test 2</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>500</v>
+      </c>
+      <c r="H6" t="n">
+        <v>144</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>356</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.447205</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.288</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>llama3.2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>zero_shot</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>facility</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Contrary(P)Body(P)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Test 3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>500</v>
+      </c>
+      <c r="H7" t="n">
+        <v>144</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>356</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.447205</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.288</v>
       </c>
     </row>
   </sheetData>
@@ -728,19 +964,19 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2</v>
+        <v>0.316</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.480243</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2</v>
+        <v>0.316</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>1500</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>474</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -749,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="3">
@@ -782,19 +1018,19 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4</v>
+        <v>0.288</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5714285714285715</v>
+        <v>0.447205</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4</v>
+        <v>0.288</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>1500</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>432</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -803,7 +1039,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>1068</v>
       </c>
     </row>
   </sheetData>
